--- a/resultados Weibull/Distribuições 8, 9 e 10.xlsx
+++ b/resultados Weibull/Distribuições 8, 9 e 10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucas Kort\Documents\GitHub\reliabilty_ml\resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kort\Documents\GitHub\reliability_ml\resultados Weibull\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA1656F-A1FC-43A4-9C0C-21B0AF58CBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CE9295-A618-4A23-8734-7BD4DB04E6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="750" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{D18CE87D-169E-4E84-B72A-2874F70A692B}"/>
+    <workbookView xWindow="-28920" yWindow="-2070" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D18CE87D-169E-4E84-B72A-2874F70A692B}"/>
   </bookViews>
   <sheets>
     <sheet name="Custo e Disponibilidade" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="60">
   <si>
     <t>Confiabilidade</t>
   </si>
@@ -212,6 +212,12 @@
   </si>
   <si>
     <t>Custo mínimo</t>
+  </si>
+  <si>
+    <t>Tempo teste</t>
+  </si>
+  <si>
+    <t>Tempo falha</t>
   </si>
 </sst>
 </file>
@@ -515,9 +521,6 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -526,15 +529,32 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="30">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -544,19 +564,26 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="0"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
     </dxf>
     <dxf>
       <font>
@@ -570,71 +597,18 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="169" formatCode="0.0000%"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -699,6 +673,32 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -724,18 +724,19 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="169" formatCode="0.0000%"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -777,6 +778,32 @@
       <numFmt numFmtId="167" formatCode="0.000000000"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="168" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
@@ -784,6 +811,32 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="168" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
@@ -930,53 +983,6 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0000"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -993,7 +999,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1387,7 +1393,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2207,7 +2213,7 @@
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2886,7 +2892,7 @@
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3754,7 +3760,7 @@
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4437,7 +4443,7 @@
 <file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5225,7 +5231,7 @@
 <file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5982,7 +5988,7 @@
 <file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6579,12 +6585,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout>
-                  <c:manualLayout>
-                    <c:x val="3.6136205698401667E-2"/>
-                    <c:y val="5.9976931949250287E-2"/>
-                  </c:manualLayout>
-                </c15:layout>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -7049,6 +7049,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="765506639"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -7137,7 +7138,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7532,7 +7533,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7932,7 +7933,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8331,7 +8332,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8731,7 +8732,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9134,7 +9135,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10047,7 +10048,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10969,7 +10970,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -21394,19 +21395,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4BF4BCB-653F-4331-ACD9-9EF26BC02590}" name="Tabela1" displayName="Tabela1" ref="F1:K6" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4BF4BCB-653F-4331-ACD9-9EF26BC02590}" name="Tabela1" displayName="Tabela1" ref="F1:K6" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="F1:K6" xr:uid="{C4BF4BCB-653F-4331-ACD9-9EF26BC02590}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{664CCFD5-13BE-48F5-831D-A81148CE5934}" name="Tempo 8" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{58A4E70C-B154-499C-A83D-16703422D9D6}" name="Confiabilidade 8" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{664CCFD5-13BE-48F5-831D-A81148CE5934}" name="Tempo 8" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{58A4E70C-B154-499C-A83D-16703422D9D6}" name="Confiabilidade 8" dataDxfId="26">
       <calculatedColumnFormula>EXP(-((F2/B$7)^(B$6)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EA735E32-B1AE-47AE-A2DA-64DF86D19A8F}" name="Tempo 9" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{49B50FFC-5863-4856-BC92-F3B65CC06D69}" name="Confiabilidade 9" dataDxfId="18">
+    <tableColumn id="3" xr3:uid="{EA735E32-B1AE-47AE-A2DA-64DF86D19A8F}" name="Tempo 9" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{49B50FFC-5863-4856-BC92-F3B65CC06D69}" name="Confiabilidade 9" dataDxfId="24">
       <calculatedColumnFormula>EXP(-((H2/C$7)^(C$6)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D679871E-1A2A-4C44-AB14-26DC8BA2ABE5}" name="Tempo 10" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{485AD8A3-FB46-416E-BDE3-440FEA41085F}" name="Confiabilidade 10" dataDxfId="16">
+    <tableColumn id="5" xr3:uid="{D679871E-1A2A-4C44-AB14-26DC8BA2ABE5}" name="Tempo 10" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{485AD8A3-FB46-416E-BDE3-440FEA41085F}" name="Confiabilidade 10" dataDxfId="22">
       <calculatedColumnFormula>EXP(-((J2/D$7)^(D$6)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -21415,7 +21416,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A2C413E4-506E-47AD-B36D-6ECB57538726}" name="Tabela11" displayName="Tabela11" ref="A36:G39" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="25" tableBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A2C413E4-506E-47AD-B36D-6ECB57538726}" name="Tabela11" displayName="Tabela11" ref="A36:G39" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A36:G39" xr:uid="{A2C413E4-506E-47AD-B36D-6ECB57538726}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{541A0F84-418B-4A14-A5DD-3BFF5AE775D1}" name="Distribuição"/>
@@ -21444,28 +21445,28 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{84629942-2D0A-4174-9586-10CCB047D8C2}" name="Tabela2" displayName="Tabela2" ref="F8:N22" totalsRowShown="0" headerRowDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{84629942-2D0A-4174-9586-10CCB047D8C2}" name="Tabela2" displayName="Tabela2" ref="F8:N22" totalsRowShown="0" headerRowDxfId="21">
   <autoFilter ref="F8:N22" xr:uid="{84629942-2D0A-4174-9586-10CCB047D8C2}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{34E80AD5-889D-4D55-A90A-12CEDE788ADC}" name="Intervalo 8" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{34E80AD5-889D-4D55-A90A-12CEDE788ADC}" name="Intervalo 8" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{D6C78803-3D69-4FA6-91F3-B8F6C5237716}" name="Confiabilidade 8">
       <calculatedColumnFormula>EXP(-((F9/B$7)^(B$6)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{FC366ABF-D588-4C80-BF15-1762DD6E9A52}" name="Custos 8" dataDxfId="13">
+    <tableColumn id="3" xr3:uid="{FC366ABF-D588-4C80-BF15-1762DD6E9A52}" name="Custos 8" dataDxfId="19">
       <calculatedColumnFormula>($B$5/F9)*($B$2*G9)+($B$5/MEDIAN(F$2:F$6)*($B$3+$B$4)*(1-G9))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{87E6A290-5C35-4F05-B116-502612F27A61}" name="Intervalo 9" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{87E6A290-5C35-4F05-B116-502612F27A61}" name="Intervalo 9" dataDxfId="18"/>
     <tableColumn id="5" xr3:uid="{A4A8B5DF-97A9-4475-BD82-4FAFCD893FF6}" name="Confiabilidade 9">
       <calculatedColumnFormula>EXP(-((I9/C$7)^(C$6)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{B48B826E-C76B-41A9-865A-451E4D31B386}" name="Custos 9" dataDxfId="12">
+    <tableColumn id="6" xr3:uid="{B48B826E-C76B-41A9-865A-451E4D31B386}" name="Custos 9" dataDxfId="17">
       <calculatedColumnFormula>($B$5/I9)*($B$2*J9)+($B$5/MEDIAN(H$2:H$6)*($B$3+$B$4)*(1-J9))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{4D43E344-18C6-427E-A208-9A819F5D59EA}" name="Intervalo 10" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{C6EE45E4-C1B5-46DB-A0F0-A60485BFFFE5}" name="Confiabilidade 10" dataDxfId="11">
+    <tableColumn id="7" xr3:uid="{4D43E344-18C6-427E-A208-9A819F5D59EA}" name="Intervalo 10" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{C6EE45E4-C1B5-46DB-A0F0-A60485BFFFE5}" name="Confiabilidade 10" dataDxfId="15">
       <calculatedColumnFormula>EXP(-((L9/D$7)^(D$6)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F5150592-17FC-4657-A213-31128D310165}" name="Custos 10" dataDxfId="10">
+    <tableColumn id="9" xr3:uid="{F5150592-17FC-4657-A213-31128D310165}" name="Custos 10" dataDxfId="14">
       <calculatedColumnFormula>($B$5/L9)*($B$2*M9)+($B$5/MEDIAN(J$2:J$6))*(($B$3+$B$4)*(1-M9))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -21474,19 +21475,19 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{88EB38B9-AE27-4A37-9665-35BB63BF85AD}" name="Tabela3" displayName="Tabela3" ref="F23:K37" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" dataCellStyle="Porcentagem">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{88EB38B9-AE27-4A37-9665-35BB63BF85AD}" name="Tabela3" displayName="Tabela3" ref="F23:K37" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="F23:K37" xr:uid="{88EB38B9-AE27-4A37-9665-35BB63BF85AD}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{CFCF50A6-6E3E-44E5-BDCA-5A01C914CF1D}" name="Intervalo 8" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{C0097A0D-EBF9-4150-AD5C-A09E4BE6A538}" name="Disponibilidade 8" dataDxfId="7" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{CFCF50A6-6E3E-44E5-BDCA-5A01C914CF1D}" name="Intervalo 8" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{C0097A0D-EBF9-4150-AD5C-A09E4BE6A538}" name="Disponibilidade 8" dataDxfId="10">
       <calculatedColumnFormula>F9/(((G9*B$9)+(1-G9)*B$10)+F9)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E0298BF7-CC76-4BDD-9CDB-0FA786CFDAB9}" name="Intervalo 9" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{C57314A9-1013-478C-9BE1-69FCA481EFEB}" name="Disponibilidade 9" dataDxfId="6" dataCellStyle="Porcentagem">
+    <tableColumn id="3" xr3:uid="{E0298BF7-CC76-4BDD-9CDB-0FA786CFDAB9}" name="Intervalo 9" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C57314A9-1013-478C-9BE1-69FCA481EFEB}" name="Disponibilidade 9" dataDxfId="8">
       <calculatedColumnFormula>I9/(((J9*C$9)+(1-J9)*C$10)+I9)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9D87930C-A537-41CD-9794-1AA8654F5869}" name="Intervalo 10" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{91634436-E407-44C7-9778-1532078177F7}" name="Disponibilidade 10" dataDxfId="5" dataCellStyle="Porcentagem">
+    <tableColumn id="5" xr3:uid="{9D87930C-A537-41CD-9794-1AA8654F5869}" name="Intervalo 10" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{91634436-E407-44C7-9778-1532078177F7}" name="Disponibilidade 10" dataDxfId="6">
       <calculatedColumnFormula>L9/(((M9*D$9)+(1-M9)*D$10)+L9)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -21499,7 +21500,7 @@
   <autoFilter ref="A1:B102" xr:uid="{E23C39F2-1327-47EE-9F16-9F6342D10460}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{08D13AE8-A4BA-4B5A-8B71-4815B64321D2}" name="Tempo"/>
-    <tableColumn id="2" xr3:uid="{D2B00276-DF3C-4798-B079-3C554E9E0E4F}" name="Confiabilidade" dataCellStyle="Porcentagem">
+    <tableColumn id="2" xr3:uid="{D2B00276-DF3C-4798-B079-3C554E9E0E4F}" name="Confiabilidade">
       <calculatedColumnFormula>EXP(-((A2/D$3)^(D$2)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -21538,7 +21539,7 @@
   <autoFilter ref="A2:F10" xr:uid="{F3D8B62F-10AB-4A1F-AC9A-05BD1DB36B8C}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{675C324F-C5E3-43CD-A809-80625C5548C6}" name="Restrição"/>
-    <tableColumn id="3" xr3:uid="{00857789-D9FB-4BB0-9021-F81F3BF4F86A}" name="Custo" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00857789-D9FB-4BB0-9021-F81F3BF4F86A}" name="Custo" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{30D29FBD-3A11-4EAA-A6C9-36994DC08D11}" name="Intervalo"/>
     <tableColumn id="5" xr3:uid="{ADB7F68B-B104-4A37-BAEE-EAF5FDE65294}" name="Confiabilidade"/>
     <tableColumn id="6" xr3:uid="{C47B3A1B-5482-4C61-8D94-0AD39321D036}" name="Disponibilidade"/>
@@ -21553,7 +21554,7 @@
   <autoFilter ref="A12:F24" xr:uid="{34B4F5A5-0648-4B26-9B99-CFCAABC257A4}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{B8E437B3-D846-46A5-9424-E362F8CC7CB1}" name="Restrição"/>
-    <tableColumn id="3" xr3:uid="{0538C644-5521-4375-990B-8DD5106C4082}" name="Custo" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{0538C644-5521-4375-990B-8DD5106C4082}" name="Custo" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{5127D8EF-8C6A-4E5C-B70B-04306757F7D2}" name="Intervalo"/>
     <tableColumn id="5" xr3:uid="{A7CB705C-526A-4572-B556-B39BF16FC858}" name="Confiabilidade"/>
     <tableColumn id="6" xr3:uid="{1B9F22F3-FE78-47F6-A56E-E490C5D80FA7}" name="Disponibilidade"/>
@@ -21568,7 +21569,7 @@
   <autoFilter ref="A26:F34" xr:uid="{EB21DC6F-21DE-4EB1-8F97-037531818EDE}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{B39E6F95-D40A-4474-9602-3961DDC4EBF9}" name="Restrição"/>
-    <tableColumn id="3" xr3:uid="{EED38AA7-8A13-4682-B8AE-D7EBBD8CF4EF}" name="Custo" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{EED38AA7-8A13-4682-B8AE-D7EBBD8CF4EF}" name="Custo" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{7393F1C2-3C6E-4056-8E3A-67B1F852E3A7}" name="Intervalo"/>
     <tableColumn id="5" xr3:uid="{941B7A4C-E9A9-4C3B-BF5B-445BEAB0CECC}" name="Confiabilidade"/>
     <tableColumn id="6" xr3:uid="{988B4CE7-8EF1-4FC1-A7E5-5C631F66BC71}" name="Disponibilidade"/>
@@ -21579,7 +21580,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -22187,7 +22188,7 @@
         <v>29.428629538461539</v>
       </c>
       <c r="J9">
-        <f>EXP(-((I9/C$7)^(C$6)))</f>
+        <f t="shared" ref="J9:J15" si="2">EXP(-((I9/C$7)^(C$6)))</f>
         <v>0.98608016899776729</v>
       </c>
       <c r="K9" s="11">
@@ -22223,33 +22224,33 @@
         <v>8.5559143384615393</v>
       </c>
       <c r="G10">
-        <f t="shared" ref="G10:G22" si="2">EXP(-((F10/B$7)^(B$6)))</f>
+        <f t="shared" ref="G10:G22" si="3">EXP(-((F10/B$7)^(B$6)))</f>
         <v>0.97845779163641022</v>
       </c>
       <c r="H10" s="11">
-        <f t="shared" ref="H10:H22" si="3">($B$5/F10)*($B$2*G10)+($B$5/MEDIAN(F$2:F$6)*($B$3+$B$4)*(1-G10))</f>
+        <f t="shared" ref="H10:H19" si="4">($B$5/F10)*($B$2*G10)+($B$5/MEDIAN(F$2:F$6)*($B$3+$B$4)*(1-G10))</f>
         <v>10756477.159373853</v>
       </c>
       <c r="I10" s="7">
         <v>58.857259076923079</v>
       </c>
       <c r="J10">
-        <f>EXP(-((I10/C$7)^(C$6)))</f>
+        <f t="shared" si="2"/>
         <v>0.94546444334067214</v>
       </c>
       <c r="K10" s="11">
-        <f t="shared" ref="K10:K22" si="4">($B$5/I10)*($B$2*J10)+($B$5/MEDIAN(H$2:H$6)*($B$3+$B$4)*(1-J10))</f>
+        <f t="shared" ref="K10:K22" si="5">($B$5/I10)*($B$2*J10)+($B$5/MEDIAN(H$2:H$6)*($B$3+$B$4)*(1-J10))</f>
         <v>1646204.0781222254</v>
       </c>
       <c r="L10" s="7">
         <v>297.08124923076923</v>
       </c>
       <c r="M10" s="9">
-        <f t="shared" ref="M10:M22" si="5">EXP(-((L10/D$7)^(D$6)))</f>
+        <f t="shared" ref="M10:M22" si="6">EXP(-((L10/D$7)^(D$6)))</f>
         <v>0.95680227092028669</v>
       </c>
       <c r="N10" s="11">
-        <f t="shared" ref="N10:N22" si="6">($B$5/L10)*($B$2*M10)+($B$5/MEDIAN(J$2:J$6))*(($B$3+$B$4)*(1-M10))</f>
+        <f t="shared" ref="N10:N22" si="7">($B$5/L10)*($B$2*M10)+($B$5/MEDIAN(J$2:J$6))*(($B$3+$B$4)*(1-M10))</f>
         <v>329805.15518580982</v>
       </c>
       <c r="O10" s="1"/>
@@ -22276,33 +22277,33 @@
         <v>12.83387150769231</v>
       </c>
       <c r="G11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.92913321940981297</v>
       </c>
       <c r="H11" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8771415.3300136812</v>
       </c>
       <c r="I11" s="7">
         <v>88.285888615384621</v>
       </c>
       <c r="J11">
-        <f>EXP(-((I11/C$7)^(C$6)))</f>
+        <f t="shared" si="2"/>
         <v>0.88144827684178451</v>
       </c>
       <c r="K11" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1394203.7843265107</v>
       </c>
       <c r="L11" s="7">
         <v>445.62187384615379</v>
       </c>
       <c r="M11" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.88543592894894307</v>
       </c>
       <c r="N11" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>300493.80187593552</v>
       </c>
       <c r="O11" s="1"/>
@@ -22314,33 +22315,33 @@
         <v>17.111828676923079</v>
       </c>
       <c r="G12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8400987534727471</v>
       </c>
       <c r="H12" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9782394.2551153488</v>
       </c>
       <c r="I12" s="7">
         <v>117.71451815384616</v>
       </c>
       <c r="J12">
-        <f>EXP(-((I12/C$7)^(C$6)))</f>
+        <f t="shared" si="2"/>
         <v>0.79903537402795732</v>
       </c>
       <c r="K12" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1475433.8739618803</v>
       </c>
       <c r="L12" s="7">
         <v>594.16249846153846</v>
       </c>
       <c r="M12" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.7789890215707429</v>
       </c>
       <c r="N12" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>358762.50158840569</v>
       </c>
       <c r="O12" s="12"/>
@@ -22352,33 +22353,33 @@
         <v>21.389785846153849</v>
       </c>
       <c r="G13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.71154710232707385</v>
       </c>
       <c r="H13" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12802768.710466873</v>
       </c>
       <c r="I13" s="7">
         <v>147.14314769230771</v>
       </c>
       <c r="J13">
-        <f>EXP(-((I13/C$7)^(C$6)))</f>
+        <f t="shared" si="2"/>
         <v>0.70429068004034268</v>
       </c>
       <c r="K13" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1715363.5279068667</v>
       </c>
       <c r="L13" s="7">
         <v>742.70312307692302</v>
       </c>
       <c r="M13" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.64643194839821738</v>
       </c>
       <c r="N13" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>466450.74618054874</v>
       </c>
       <c r="O13" s="12"/>
@@ -22390,33 +22391,33 @@
         <v>25.66774301538462</v>
       </c>
       <c r="G14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.55539531056617375</v>
       </c>
       <c r="H14" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17137334.464237105</v>
       </c>
       <c r="I14" s="7">
         <v>176.57177723076924</v>
       </c>
       <c r="J14">
-        <f>EXP(-((I14/C$7)^(C$6)))</f>
+        <f t="shared" si="2"/>
         <v>0.60360667991927053</v>
       </c>
       <c r="K14" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2036821.2502637329</v>
       </c>
       <c r="L14" s="7">
         <v>891.24374769230758</v>
       </c>
       <c r="M14" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.50248547381214048</v>
       </c>
       <c r="N14" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>598457.37766083318</v>
       </c>
       <c r="O14" s="12"/>
@@ -22432,44 +22433,44 @@
         <v>4.2779571692307696</v>
       </c>
       <c r="D15">
-        <f t="shared" ref="D15:E15" si="7">C$11*(2*($B15/$B$27))</f>
+        <f t="shared" ref="D15:E15" si="8">C$11*(2*($B15/$B$27))</f>
         <v>29.428629538461539</v>
       </c>
       <c r="E15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>148.54062461538462</v>
       </c>
       <c r="F15" s="8">
         <v>29.945700184615387</v>
       </c>
       <c r="G15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.39303398510199439</v>
       </c>
       <c r="H15" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21957638.612083849</v>
       </c>
       <c r="I15" s="8">
         <v>206.00040676923075</v>
       </c>
       <c r="J15">
-        <f>EXP(-((I15/C$7)^(C$6)))</f>
+        <f t="shared" si="2"/>
         <v>0.50300442400685186</v>
       </c>
       <c r="K15" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2392193.3987830915</v>
       </c>
       <c r="L15" s="8">
         <v>1039.7843723076921</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.36359423611927311</v>
       </c>
       <c r="N15" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>732983.95925005362</v>
       </c>
       <c r="O15" s="12"/>
@@ -22481,48 +22482,48 @@
         <v>2</v>
       </c>
       <c r="C16">
-        <f t="shared" ref="C16:E16" si="8">B$11*(2*($B16/$B$27))</f>
+        <f t="shared" ref="C16:E16" si="9">B$11*(2*($B16/$B$27))</f>
         <v>8.5559143384615393</v>
       </c>
       <c r="D16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>58.857259076923079</v>
       </c>
       <c r="E16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>297.08124923076923</v>
       </c>
       <c r="F16" s="7">
         <v>34.223657353846157</v>
       </c>
       <c r="G16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.24807974070171143</v>
       </c>
       <c r="H16" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>26412186.424304198</v>
       </c>
       <c r="I16" s="7">
         <v>235.42903630769231</v>
       </c>
       <c r="J16" s="2">
-        <f t="shared" ref="J16:J21" si="9">EXP(-((I16/C$7)^(C$6)))</f>
+        <f t="shared" ref="J16:J21" si="10">EXP(-((I16/C$7)^(C$6)))</f>
         <v>0.40757245979834406</v>
       </c>
       <c r="K16" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2748218.3623261135</v>
       </c>
       <c r="L16" s="7">
         <v>1188.3249969230769</v>
       </c>
       <c r="M16" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.24350441159474134</v>
       </c>
       <c r="N16" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>852836.09589643008</v>
       </c>
       <c r="O16" s="1"/>
@@ -22534,48 +22535,48 @@
         <v>3</v>
       </c>
       <c r="C17">
-        <f t="shared" ref="C17:E17" si="10">B$11*(2*($B17/$B$27))</f>
+        <f t="shared" ref="C17:E17" si="11">B$11*(2*($B17/$B$27))</f>
         <v>12.83387150769231</v>
       </c>
       <c r="D17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>88.285888615384621</v>
       </c>
       <c r="E17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>445.62187384615379</v>
       </c>
       <c r="F17" s="7">
         <v>38.501614523076924</v>
       </c>
       <c r="G17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.13740091431060436</v>
       </c>
       <c r="H17" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29884083.298306573</v>
       </c>
       <c r="I17" s="7">
         <v>264.85766584615385</v>
       </c>
       <c r="J17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.32110920615592714</v>
       </c>
       <c r="K17" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3081732.9812665568</v>
       </c>
       <c r="L17" s="7">
         <v>1336.8656215384613</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.15013100497902332</v>
       </c>
       <c r="N17" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>947772.17807765282</v>
       </c>
       <c r="O17" s="1"/>
@@ -22587,48 +22588,48 @@
         <v>4</v>
       </c>
       <c r="C18">
-        <f t="shared" ref="C18:E18" si="11">B$11*(2*($B18/$B$27))</f>
+        <f t="shared" ref="C18:E18" si="12">B$11*(2*($B18/$B$27))</f>
         <v>17.111828676923079</v>
       </c>
       <c r="D18">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>117.71451815384616</v>
       </c>
       <c r="E18">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>594.16249846153846</v>
       </c>
       <c r="F18" s="7">
         <v>42.779571692307698</v>
       </c>
       <c r="G18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.5694467464322392E-2</v>
       </c>
       <c r="H18" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>32164215.042835187</v>
       </c>
       <c r="I18" s="7">
         <v>294.28629538461541</v>
       </c>
       <c r="J18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.24598876315081694</v>
       </c>
       <c r="K18" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3377998.7921709288</v>
       </c>
       <c r="L18" s="7">
         <v>1485.406246153846</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.4786516592999225E-2</v>
       </c>
       <c r="N18" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1015050.4673928233</v>
       </c>
       <c r="O18" s="1"/>
@@ -22640,48 +22641,48 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <f t="shared" ref="C19:E19" si="12">B$11*(2*($B19/$B$27))</f>
+        <f t="shared" ref="C19:E19" si="13">B$11*(2*($B19/$B$27))</f>
         <v>21.389785846153849</v>
       </c>
       <c r="D19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>147.14314769230771</v>
       </c>
       <c r="E19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>742.70312307692302</v>
       </c>
       <c r="F19" s="7">
         <v>47.057528861538465</v>
       </c>
       <c r="G19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.6675492429130518E-2</v>
       </c>
       <c r="H19" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>33416991.25504167</v>
       </c>
       <c r="I19" s="7">
         <v>323.71492492307692</v>
       </c>
       <c r="J19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.18322810264893136</v>
       </c>
       <c r="K19" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3629433.8950120625</v>
       </c>
       <c r="L19" s="7">
         <v>1633.9468707692306</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.3652963516474998E-2</v>
       </c>
       <c r="N19" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1057786.551289618</v>
       </c>
       <c r="O19" s="1"/>
@@ -22693,22 +22694,22 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <f t="shared" ref="C20:E20" si="13">B$11*(2*($B20/$B$27))</f>
+        <f t="shared" ref="C20:E20" si="14">B$11*(2*($B20/$B$27))</f>
         <v>25.66774301538462</v>
       </c>
       <c r="D20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>176.57177723076924</v>
       </c>
       <c r="E20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>891.24374769230758</v>
       </c>
       <c r="F20" s="7">
         <v>51.335486030769239</v>
       </c>
       <c r="G20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.0499067895011345E-3</v>
       </c>
       <c r="H20" s="11">
@@ -22719,22 +22720,22 @@
         <v>353.14355446153849</v>
       </c>
       <c r="J20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.13270367463346744</v>
       </c>
       <c r="K20" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3834213.8267011582</v>
       </c>
       <c r="L20" s="7">
         <v>1782.4874953846152</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.0397173308347172E-2</v>
       </c>
       <c r="N20" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1082114.2369922921</v>
       </c>
       <c r="O20" s="1"/>
@@ -22746,48 +22747,48 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <f t="shared" ref="C21:E21" si="14">B$11*(2*($B21/$B$27))</f>
+        <f t="shared" ref="C21:E21" si="15">B$11*(2*($B21/$B$27))</f>
         <v>29.945700184615387</v>
       </c>
       <c r="D21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>206.00040676923075</v>
       </c>
       <c r="E21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1039.7843723076921</v>
       </c>
       <c r="F21" s="7">
         <v>55.613443200000006</v>
       </c>
       <c r="G21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5236390401234309E-3</v>
       </c>
       <c r="H21" s="11">
-        <f t="shared" ref="H21:H22" si="15">($B$5/F21)*($B$2*G21)+($B$5/MEDIAN(F$2:F$6)*($B$3+$B$4)*(1-G21))</f>
+        <f t="shared" ref="H21:H22" si="16">($B$5/F21)*($B$2*G21)+($B$5/MEDIAN(F$2:F$6)*($B$3+$B$4)*(1-G21))</f>
         <v>34199278.029935673</v>
       </c>
       <c r="I21" s="7">
         <v>382.57218399999999</v>
       </c>
       <c r="J21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.345179109747459E-2</v>
       </c>
       <c r="K21" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3994732.006955443</v>
       </c>
       <c r="L21" s="7">
         <v>1931.0281199999997</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.6123534509679762E-3</v>
       </c>
       <c r="N21" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1094508.5100133664</v>
       </c>
       <c r="O21" s="1"/>
@@ -22802,29 +22803,29 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <f t="shared" ref="C22:E22" si="16">B$11*(2*($B22/$B$27))</f>
+        <f t="shared" ref="C22:E22" si="17">B$11*(2*($B22/$B$27))</f>
         <v>34.223657353846157</v>
       </c>
       <c r="D22">
+        <f t="shared" si="17"/>
+        <v>235.42903630769231</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="17"/>
+        <v>1188.3249969230769</v>
+      </c>
+      <c r="F22" s="42">
+        <v>270</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="3"/>
+        <v>4.4480038711946786E-298</v>
+      </c>
+      <c r="H22" s="11">
         <f t="shared" si="16"/>
-        <v>235.42903630769231</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="16"/>
-        <v>1188.3249969230769</v>
-      </c>
-      <c r="F22" s="43">
-        <v>270</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="2"/>
-        <v>4.4480038711946786E-298</v>
-      </c>
-      <c r="H22" s="11">
-        <f t="shared" si="15"/>
         <v>34281817.831742331</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="42">
         <v>1910</v>
       </c>
       <c r="J22">
@@ -22832,18 +22833,18 @@
         <v>2.1506638167138473E-26</v>
       </c>
       <c r="K22" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4382926.0414252551</v>
       </c>
-      <c r="L22" s="43">
+      <c r="L22" s="42">
         <v>9650</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.8374725879470338E-116</v>
       </c>
       <c r="N22" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1103622.6034003671</v>
       </c>
       <c r="O22" s="1"/>
@@ -22855,15 +22856,15 @@
         <v>9</v>
       </c>
       <c r="C23">
-        <f t="shared" ref="C23:E23" si="17">B$11*(2*($B23/$B$27))</f>
+        <f t="shared" ref="C23:E23" si="18">B$11*(2*($B23/$B$27))</f>
         <v>38.501614523076924</v>
       </c>
       <c r="D23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>264.85766584615385</v>
       </c>
       <c r="E23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1336.8656215384613</v>
       </c>
       <c r="F23" s="20" t="s">
@@ -22895,15 +22896,15 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <f t="shared" ref="C24:E24" si="18">B$11*(2*($B24/$B$27))</f>
+        <f t="shared" ref="C24:E24" si="19">B$11*(2*($B24/$B$27))</f>
         <v>42.779571692307698</v>
       </c>
       <c r="D24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>294.28629538461541</v>
       </c>
       <c r="E24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1485.406246153846</v>
       </c>
       <c r="F24" s="7">
@@ -22942,11 +22943,11 @@
         <v>11</v>
       </c>
       <c r="C25">
-        <f t="shared" ref="C25:E25" si="19">B$11*(2*($B25/$B$27))</f>
+        <f t="shared" ref="C25:D25" si="20">B$11*(2*($B25/$B$27))</f>
         <v>47.057528861538465</v>
       </c>
       <c r="D25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>323.71492492307692</v>
       </c>
       <c r="E25">
@@ -22958,7 +22959,7 @@
         <v>7.9852825000000003</v>
       </c>
       <c r="G25" s="10">
-        <f t="shared" ref="G25:G37" si="20">F10/(((G10*B$9)+(1-G10)*B$10)+F10)</f>
+        <f t="shared" ref="G25:G37" si="21">F10/(((G10*B$9)+(1-G10)*B$10)+F10)</f>
         <v>0.94142825939374353</v>
       </c>
       <c r="H25" s="7">
@@ -22966,7 +22967,7 @@
         <v>8.0494906660521615E-2</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" ref="I25:I37" si="21">I10/(((J10*C$9)+(1-J10)*C$10)+I10)</f>
+        <f t="shared" ref="I25:I37" si="22">I10/(((J10*C$9)+(1-J10)*C$10)+I10)</f>
         <v>0.90293373398052412</v>
       </c>
       <c r="J25" s="7">
@@ -22974,7 +22975,7 @@
         <v>62.458275</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" ref="K25:K37" si="22">L10/(((M10*D$9)+(1-M10)*D$10)+L10)</f>
+        <f t="shared" ref="K25:K37" si="23">L10/(((M10*D$9)+(1-M10)*D$10)+L10)</f>
         <v>0.9844546304937043</v>
       </c>
     </row>
@@ -22983,15 +22984,15 @@
         <v>12</v>
       </c>
       <c r="C26">
-        <f t="shared" ref="C26:E26" si="23">B$11*(2*($B26/$B$27))</f>
+        <f t="shared" ref="C26:E26" si="24">B$11*(2*($B26/$B$27))</f>
         <v>51.335486030769239</v>
       </c>
       <c r="D26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>353.14355446153849</v>
       </c>
       <c r="E26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1782.4874953846152</v>
       </c>
       <c r="F26" s="7">
@@ -22999,7 +23000,7 @@
         <v>11.1793955</v>
       </c>
       <c r="G26" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.95488895637756865</v>
       </c>
       <c r="H26" s="7">
@@ -23007,7 +23008,7 @@
         <v>0.11269286932473026</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.92935254499266362</v>
       </c>
       <c r="J26" s="7">
@@ -23015,7 +23016,7 @@
         <v>87.441584999999989</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.98707949531623773</v>
       </c>
     </row>
@@ -23024,15 +23025,15 @@
         <v>13</v>
       </c>
       <c r="C27">
-        <f t="shared" ref="C27:E27" si="24">B$11*(2*($B27/$B$27))</f>
+        <f t="shared" ref="C27:E27" si="25">B$11*(2*($B27/$B$27))</f>
         <v>55.613443200000006</v>
       </c>
       <c r="D27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>382.57218399999999</v>
       </c>
       <c r="E27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1931.0281199999997</v>
       </c>
       <c r="F27" s="7">
@@ -23040,7 +23041,7 @@
         <v>15.970565000000001</v>
       </c>
       <c r="G27" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.95855561789519772</v>
       </c>
       <c r="H27" s="7">
@@ -23048,7 +23049,7 @@
         <v>0.16098981332104323</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.9423169219498847</v>
       </c>
       <c r="J27" s="7">
@@ -23056,7 +23057,7 @@
         <v>124.91655</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.98747516659242274</v>
       </c>
     </row>
@@ -23066,7 +23067,7 @@
         <v>19.164677999999999</v>
       </c>
       <c r="G28" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.95821790566321796</v>
       </c>
       <c r="H28" s="7">
@@ -23074,7 +23075,7 @@
         <v>0.19318777598525186</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.94981676855864605</v>
       </c>
       <c r="J28" s="7">
@@ -23082,7 +23083,7 @@
         <v>149.89985999999999</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.98716427494057946</v>
       </c>
     </row>
@@ -23092,7 +23093,7 @@
         <v>23.955847500000001</v>
       </c>
       <c r="G29" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.95651491515646037</v>
       </c>
       <c r="H29" s="7">
@@ -23100,7 +23101,7 @@
         <v>0.24148471998156484</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.95469935816466855</v>
       </c>
       <c r="J29" s="7">
@@ -23108,7 +23109,7 @@
         <v>187.37482499999999</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.98675799411608911</v>
       </c>
     </row>
@@ -23118,7 +23119,7 @@
         <v>31.941130000000001</v>
       </c>
       <c r="G30" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.95501842356223288</v>
       </c>
       <c r="H30" s="8">
@@ -23126,7 +23127,7 @@
         <v>0.32197962664208646</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.95821995529796222</v>
       </c>
       <c r="J30" s="8">
@@ -23134,7 +23135,7 @@
         <v>249.8331</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.98654370198970243</v>
       </c>
     </row>
@@ -23144,7 +23145,7 @@
         <v>39.926412499999998</v>
       </c>
       <c r="G31" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.95459384753239362</v>
       </c>
       <c r="H31" s="7">
@@ -23152,7 +23153,7 @@
         <v>0.40247453330260807</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.96099916410404029</v>
       </c>
       <c r="J31" s="7">
@@ -23160,7 +23161,7 @@
         <v>312.29137500000002</v>
       </c>
       <c r="K31" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.98662940663219278</v>
       </c>
     </row>
@@ -23170,7 +23171,7 @@
         <v>43.120525500000007</v>
       </c>
       <c r="G32" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.95548142986082374</v>
       </c>
       <c r="H32" s="7">
@@ -23178,7 +23179,7 @@
         <v>0.43467249596681673</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.96336046362779171</v>
       </c>
       <c r="J32" s="7">
@@ -23186,7 +23187,7 @@
         <v>337.27468500000003</v>
       </c>
       <c r="K32" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.98700747300347214</v>
       </c>
     </row>
@@ -23196,7 +23197,7 @@
         <v>47.911695000000002</v>
       </c>
       <c r="G33" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.95744372277940337</v>
       </c>
       <c r="H33" s="7">
@@ -23204,7 +23205,7 @@
         <v>0.48296943996312969</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.96547339360701712</v>
       </c>
       <c r="J33" s="7">
@@ -23212,7 +23213,7 @@
         <v>374.74964999999997</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.98760452117578024</v>
       </c>
     </row>
@@ -23222,7 +23223,7 @@
         <v>51.105808000000003</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.96001456343819991</v>
       </c>
       <c r="H34" s="7">
@@ -23230,7 +23231,7 @@
         <v>0.5151674026273384</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.96742341717639857</v>
       </c>
       <c r="J34" s="7">
@@ -23238,7 +23239,7 @@
         <v>399.73296000000005</v>
       </c>
       <c r="K34" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.98832507425315386</v>
       </c>
     </row>
@@ -23248,7 +23249,7 @@
         <v>55.896977500000006</v>
       </c>
       <c r="G35" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.96274655022283673</v>
       </c>
       <c r="H35" s="7">
@@ -23256,7 +23257,7 @@
         <v>0.5634643466236513</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.96924973245178958</v>
       </c>
       <c r="J35" s="7">
@@ -23264,7 +23265,7 @@
         <v>437.20792499999999</v>
       </c>
       <c r="K35" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.98908330404883282</v>
       </c>
     </row>
@@ -23274,7 +23275,7 @@
         <v>63.882260000000002</v>
       </c>
       <c r="G36" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.96534930739566094</v>
       </c>
       <c r="H36" s="7">
@@ -23282,7 +23283,7 @@
         <v>0.64395925328417292</v>
       </c>
       <c r="I36" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.97096711636603084</v>
       </c>
       <c r="J36" s="7">
@@ -23290,30 +23291,30 @@
         <v>499.6662</v>
       </c>
       <c r="K36" s="10">
+        <f t="shared" si="23"/>
+        <v>0.98981890364758585</v>
+      </c>
+    </row>
+    <row r="37" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F37" s="42">
+        <v>270</v>
+      </c>
+      <c r="G37" s="10">
+        <f t="shared" si="21"/>
+        <v>0.99264705882352944</v>
+      </c>
+      <c r="H37" s="42">
+        <v>1910</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="22"/>
-        <v>0.98981890364758585</v>
-      </c>
-    </row>
-    <row r="37" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F37" s="43">
-        <v>270</v>
-      </c>
-      <c r="G37" s="10">
-        <f t="shared" si="20"/>
-        <v>0.99264705882352944</v>
-      </c>
-      <c r="H37" s="43">
-        <v>1910</v>
-      </c>
-      <c r="I37" s="10">
-        <f t="shared" si="21"/>
         <v>0.99375650364203949</v>
       </c>
-      <c r="J37" s="43">
+      <c r="J37" s="42">
         <v>9650</v>
       </c>
       <c r="K37" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.99793174767321613</v>
       </c>
     </row>
@@ -25225,21 +25226,27 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8BBCAC-F3B4-4BCF-B387-EB3A4E785569}">
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -25253,8 +25260,22 @@
       <c r="D2" s="13">
         <v>2.4997690000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F2">
+        <v>300</v>
+      </c>
+      <c r="G2" s="27">
+        <f>EXP(-((F2/D$3)^(D$2)))</f>
+        <v>0.955757480407876</v>
+      </c>
+      <c r="I2">
+        <v>300</v>
+      </c>
+      <c r="J2">
+        <f>(D2/D3)*((I2/D3)^(D2-1))</f>
+        <v>3.770574874608914E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>120.5469845507603</v>
       </c>
@@ -25268,8 +25289,24 @@
       <c r="D3" s="14">
         <v>1034.95</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F3">
+        <f>G2</f>
+        <v>0.955757480407876</v>
+      </c>
+      <c r="G3">
+        <f>-LN(F3)^(1/D2)*D3</f>
+        <v>299.99999999999994</v>
+      </c>
+      <c r="I3">
+        <f>J2</f>
+        <v>3.770574874608914E-4</v>
+      </c>
+      <c r="J3">
+        <f>D3*((I3*D3/D2)^(1/(D2-1)))</f>
+        <v>300.00000000000006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>174.09374463825949</v>
       </c>
@@ -25278,7 +25315,7 @@
         <v>0.98845697478066463</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>269.98390361417052</v>
       </c>
@@ -25287,7 +25324,7 @@
         <v>0.9658293577695003</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>281.42302267764711</v>
       </c>
@@ -25296,7 +25333,7 @@
         <v>0.96216591957865283</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>329.67476124925332</v>
       </c>
@@ -25305,7 +25342,7 @@
         <v>0.94432618388139478</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>331.10033752862438</v>
       </c>
@@ -25314,7 +25351,7 @@
         <v>0.94373973606557437</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>342.7431371756914</v>
       </c>
@@ -25323,7 +25360,7 @@
         <v>0.9388216133033892</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>369.71986817432992</v>
       </c>
@@ -25332,7 +25369,7 @@
         <v>0.92654434302291133</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>385.84083163702638</v>
       </c>
@@ -25341,7 +25378,7 @@
         <v>0.91861970167960538</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>430.30824700732012</v>
       </c>
@@ -25350,7 +25387,7 @@
         <v>0.89449967512635864</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>439.68729436753762</v>
       </c>
@@ -25359,7 +25396,7 @@
         <v>0.88899382799544679</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>469.71043004073869</v>
       </c>
@@ -25368,7 +25405,7 @@
         <v>0.87041130584418114</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>499.82467001646808</v>
       </c>
@@ -25377,7 +25414,7 @@
         <v>0.85034480082208141</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>530.51937634423348</v>
       </c>
@@ -26183,14 +26220,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
       <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
@@ -26395,14 +26432,14 @@
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
       <c r="G11" s="33"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
@@ -26679,14 +26716,14 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -26879,14 +26916,14 @@
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="42" t="s">
+      <c r="A35" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="42"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -27069,40 +27106,40 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" s="44"/>
-      <c r="B66" s="44"/>
-      <c r="C66" s="44"/>
-      <c r="D66" s="44"/>
-      <c r="E66" s="44"/>
-      <c r="F66" s="44"/>
-      <c r="G66" s="44"/>
+      <c r="A66" s="43"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="43"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" s="45"/>
-      <c r="B67" s="46"/>
-      <c r="C67" s="47"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="47"/>
+      <c r="A67" s="44"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="46"/>
+      <c r="D67" s="45"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="45"/>
+      <c r="G67" s="46"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="45"/>
-      <c r="B68" s="46"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="47"/>
+      <c r="A68" s="44"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="45"/>
+      <c r="D68" s="45"/>
+      <c r="E68" s="45"/>
+      <c r="F68" s="45"/>
+      <c r="G68" s="46"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="12"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
+      <c r="B69" s="46"/>
+      <c r="C69" s="46"/>
+      <c r="D69" s="46"/>
+      <c r="E69" s="46"/>
+      <c r="F69" s="46"/>
+      <c r="G69" s="46"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B77" s="29"/>
@@ -27120,14 +27157,14 @@
       <c r="D79" s="29"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B80" s="48"/>
-      <c r="C80" s="48"/>
-      <c r="D80" s="48"/>
+      <c r="B80" s="47"/>
+      <c r="C80" s="47"/>
+      <c r="D80" s="47"/>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B81" s="48"/>
-      <c r="C81" s="48"/>
-      <c r="D81" s="48"/>
+      <c r="B81" s="47"/>
+      <c r="C81" s="47"/>
+      <c r="D81" s="47"/>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B82" s="29"/>

--- a/resultados Weibull/Distribuições 8, 9 e 10.xlsx
+++ b/resultados Weibull/Distribuições 8, 9 e 10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kort\Documents\GitHub\reliability_ml\resultados Weibull\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kort\Documents\GitHub\OCM\resultados Weibull\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CE9295-A618-4A23-8734-7BD4DB04E6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE67C38-D958-4D9D-AF35-E689E0016A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2070" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D18CE87D-169E-4E84-B72A-2874F70A692B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D18CE87D-169E-4E84-B72A-2874F70A692B}"/>
   </bookViews>
   <sheets>
     <sheet name="Custo e Disponibilidade" sheetId="1" r:id="rId1"/>
@@ -8444,43 +8444,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>3.219796266420865E-2</c:v>
+                  <c:v>24.983310000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.0494906660521615E-2</c:v>
+                  <c:v>62.458275</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.11269286932473026</c:v>
+                  <c:v>87.441584999999989</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.16098981332104323</c:v>
+                  <c:v>124.91655</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.19318777598525186</c:v>
+                  <c:v>149.89985999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.24148471998156484</c:v>
+                  <c:v>187.37482499999999</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="#,##0.0000">
-                  <c:v>0.32197962664208646</c:v>
+                  <c:v>249.8331</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.40247453330260807</c:v>
+                  <c:v>312.29137500000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.43467249596681673</c:v>
+                  <c:v>337.27468500000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.48296943996312969</c:v>
+                  <c:v>374.74964999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5151674026273384</c:v>
+                  <c:v>399.73296000000005</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5634643466236513</c:v>
+                  <c:v>437.20792499999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.64395925328417292</c:v>
+                  <c:v>499.6662</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8847,43 +8847,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>24.983310000000003</c:v>
+                  <c:v>99.218700000000013</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>62.458275</c:v>
+                  <c:v>248.04675</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>87.441584999999989</c:v>
+                  <c:v>347.26544999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>124.91655</c:v>
+                  <c:v>496.09350000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>149.89985999999999</c:v>
+                  <c:v>595.31219999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>187.37482499999999</c:v>
+                  <c:v>744.14025000000004</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="#,##0.0000">
-                  <c:v>249.8331</c:v>
+                  <c:v>992.18700000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>312.29137500000002</c:v>
+                  <c:v>1240.2337500000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>337.27468500000003</c:v>
+                  <c:v>1339.45245</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>374.74964999999997</c:v>
+                  <c:v>1488.2805000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>399.73296000000005</c:v>
+                  <c:v>1587.4992000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>437.20792499999999</c:v>
+                  <c:v>1736.32725</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>499.6662</c:v>
+                  <c:v>1984.374</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -22916,16 +22916,16 @@
         <v>0.89458934293464332</v>
       </c>
       <c r="H24" s="7">
-        <f>0.1*MEDIAN(G$2:G$6)</f>
-        <v>3.219796266420865E-2</v>
+        <f>0.1*MEDIAN(H$2:H$6)</f>
+        <v>24.983310000000003</v>
       </c>
       <c r="I24" s="10">
         <f>I9/(((J9*C$9)+(1-J9)*C$10)+I9)</f>
         <v>0.8286918916826268</v>
       </c>
       <c r="J24" s="7">
-        <f>0.1*MEDIAN(H$2:H$6)</f>
-        <v>24.983310000000003</v>
+        <f>0.1*MEDIAN(J$2:J$6)</f>
+        <v>99.218700000000013</v>
       </c>
       <c r="K24" s="10">
         <f>L9/(((M9*D$9)+(1-M9)*D$10)+L9)</f>
@@ -22963,16 +22963,16 @@
         <v>0.94142825939374353</v>
       </c>
       <c r="H25" s="7">
-        <f>0.25*MEDIAN(G$2:G$6)</f>
-        <v>8.0494906660521615E-2</v>
+        <f>0.25*MEDIAN(H$2:H$6)</f>
+        <v>62.458275</v>
       </c>
       <c r="I25" s="10">
         <f t="shared" ref="I25:I37" si="22">I10/(((J10*C$9)+(1-J10)*C$10)+I10)</f>
         <v>0.90293373398052412</v>
       </c>
       <c r="J25" s="7">
-        <f>0.25*MEDIAN(H$2:H$6)</f>
-        <v>62.458275</v>
+        <f>0.25*MEDIAN(J$2:J$6)</f>
+        <v>248.04675</v>
       </c>
       <c r="K25" s="10">
         <f t="shared" ref="K25:K37" si="23">L10/(((M10*D$9)+(1-M10)*D$10)+L10)</f>
@@ -23004,16 +23004,16 @@
         <v>0.95488895637756865</v>
       </c>
       <c r="H26" s="7">
-        <f>0.35*MEDIAN(G$2:G$6)</f>
-        <v>0.11269286932473026</v>
+        <f>0.35*MEDIAN(H$2:H$6)</f>
+        <v>87.441584999999989</v>
       </c>
       <c r="I26" s="10">
         <f t="shared" si="22"/>
         <v>0.92935254499266362</v>
       </c>
       <c r="J26" s="7">
-        <f>0.35*MEDIAN(H$2:H$6)</f>
-        <v>87.441584999999989</v>
+        <f>0.35*MEDIAN(J$2:J$6)</f>
+        <v>347.26544999999999</v>
       </c>
       <c r="K26" s="10">
         <f t="shared" si="23"/>
@@ -23045,16 +23045,16 @@
         <v>0.95855561789519772</v>
       </c>
       <c r="H27" s="7">
-        <f>0.5*MEDIAN(G$2:G$6)</f>
-        <v>0.16098981332104323</v>
+        <f>0.5*MEDIAN(H$2:H$6)</f>
+        <v>124.91655</v>
       </c>
       <c r="I27" s="10">
         <f t="shared" si="22"/>
         <v>0.9423169219498847</v>
       </c>
       <c r="J27" s="7">
-        <f>0.5*MEDIAN(H$2:H$6)</f>
-        <v>124.91655</v>
+        <f>0.5*MEDIAN(J$2:J$6)</f>
+        <v>496.09350000000001</v>
       </c>
       <c r="K27" s="10">
         <f t="shared" si="23"/>
@@ -23071,16 +23071,16 @@
         <v>0.95821790566321796</v>
       </c>
       <c r="H28" s="7">
-        <f>0.6*MEDIAN(G$2:G$6)</f>
-        <v>0.19318777598525186</v>
+        <f>0.6*MEDIAN(H$2:H$6)</f>
+        <v>149.89985999999999</v>
       </c>
       <c r="I28" s="10">
         <f t="shared" si="22"/>
         <v>0.94981676855864605</v>
       </c>
       <c r="J28" s="7">
-        <f>0.6*MEDIAN(H$2:H$6)</f>
-        <v>149.89985999999999</v>
+        <f>0.6*MEDIAN(J$2:J$6)</f>
+        <v>595.31219999999996</v>
       </c>
       <c r="K28" s="10">
         <f t="shared" si="23"/>
@@ -23097,16 +23097,16 @@
         <v>0.95651491515646037</v>
       </c>
       <c r="H29" s="7">
-        <f>0.75*MEDIAN(G$2:G$6)</f>
-        <v>0.24148471998156484</v>
+        <f>0.75*MEDIAN(H$2:H$6)</f>
+        <v>187.37482499999999</v>
       </c>
       <c r="I29" s="10">
         <f t="shared" si="22"/>
         <v>0.95469935816466855</v>
       </c>
       <c r="J29" s="7">
-        <f>0.75*MEDIAN(H$2:H$6)</f>
-        <v>187.37482499999999</v>
+        <f>0.75*MEDIAN(J$2:J$6)</f>
+        <v>744.14025000000004</v>
       </c>
       <c r="K29" s="10">
         <f t="shared" si="23"/>
@@ -23123,16 +23123,16 @@
         <v>0.95501842356223288</v>
       </c>
       <c r="H30" s="8">
-        <f>MEDIAN(G$2:G$6)</f>
-        <v>0.32197962664208646</v>
+        <f>MEDIAN(H$2:H$6)</f>
+        <v>249.8331</v>
       </c>
       <c r="I30" s="10">
         <f t="shared" si="22"/>
         <v>0.95821995529796222</v>
       </c>
       <c r="J30" s="8">
-        <f>MEDIAN(H$2:H$6)</f>
-        <v>249.8331</v>
+        <f>MEDIAN(J$2:J$6)</f>
+        <v>992.18700000000001</v>
       </c>
       <c r="K30" s="10">
         <f t="shared" si="23"/>
@@ -23149,16 +23149,16 @@
         <v>0.95459384753239362</v>
       </c>
       <c r="H31" s="7">
-        <f>1.25*MEDIAN(G$2:G$6)</f>
-        <v>0.40247453330260807</v>
+        <f>1.25*MEDIAN(H$2:H$6)</f>
+        <v>312.29137500000002</v>
       </c>
       <c r="I31" s="10">
         <f t="shared" si="22"/>
         <v>0.96099916410404029</v>
       </c>
       <c r="J31" s="7">
-        <f>1.25*MEDIAN(H$2:H$6)</f>
-        <v>312.29137500000002</v>
+        <f>1.25*MEDIAN(J$2:J$6)</f>
+        <v>1240.2337500000001</v>
       </c>
       <c r="K31" s="10">
         <f t="shared" si="23"/>
@@ -23175,16 +23175,16 @@
         <v>0.95548142986082374</v>
       </c>
       <c r="H32" s="7">
-        <f>1.35*MEDIAN(G$2:G$6)</f>
-        <v>0.43467249596681673</v>
+        <f>1.35*MEDIAN(H$2:H$6)</f>
+        <v>337.27468500000003</v>
       </c>
       <c r="I32" s="10">
         <f t="shared" si="22"/>
         <v>0.96336046362779171</v>
       </c>
       <c r="J32" s="7">
-        <f>1.35*MEDIAN(H$2:H$6)</f>
-        <v>337.27468500000003</v>
+        <f>1.35*MEDIAN(J$2:J$6)</f>
+        <v>1339.45245</v>
       </c>
       <c r="K32" s="10">
         <f t="shared" si="23"/>
@@ -23201,16 +23201,16 @@
         <v>0.95744372277940337</v>
       </c>
       <c r="H33" s="7">
-        <f>1.5*MEDIAN(G$2:G$6)</f>
-        <v>0.48296943996312969</v>
+        <f>1.5*MEDIAN(H$2:H$6)</f>
+        <v>374.74964999999997</v>
       </c>
       <c r="I33" s="10">
         <f t="shared" si="22"/>
         <v>0.96547339360701712</v>
       </c>
       <c r="J33" s="7">
-        <f>1.5*MEDIAN(H$2:H$6)</f>
-        <v>374.74964999999997</v>
+        <f>1.5*MEDIAN(J$2:J$6)</f>
+        <v>1488.2805000000001</v>
       </c>
       <c r="K33" s="10">
         <f t="shared" si="23"/>
@@ -23227,16 +23227,16 @@
         <v>0.96001456343819991</v>
       </c>
       <c r="H34" s="7">
-        <f>1.6*MEDIAN(G$2:G$6)</f>
-        <v>0.5151674026273384</v>
+        <f>1.6*MEDIAN(H$2:H$6)</f>
+        <v>399.73296000000005</v>
       </c>
       <c r="I34" s="10">
         <f t="shared" si="22"/>
         <v>0.96742341717639857</v>
       </c>
       <c r="J34" s="7">
-        <f>1.6*MEDIAN(H$2:H$6)</f>
-        <v>399.73296000000005</v>
+        <f>1.6*MEDIAN(J$2:J$6)</f>
+        <v>1587.4992000000002</v>
       </c>
       <c r="K34" s="10">
         <f t="shared" si="23"/>
@@ -23253,16 +23253,16 @@
         <v>0.96274655022283673</v>
       </c>
       <c r="H35" s="7">
-        <f>1.75*MEDIAN(G$2:G$6)</f>
-        <v>0.5634643466236513</v>
+        <f>1.75*MEDIAN(H$2:H$6)</f>
+        <v>437.20792499999999</v>
       </c>
       <c r="I35" s="10">
         <f t="shared" si="22"/>
         <v>0.96924973245178958</v>
       </c>
       <c r="J35" s="7">
-        <f>1.75*MEDIAN(H$2:H$6)</f>
-        <v>437.20792499999999</v>
+        <f>1.75*MEDIAN(J$2:J$6)</f>
+        <v>1736.32725</v>
       </c>
       <c r="K35" s="10">
         <f t="shared" si="23"/>
@@ -23279,16 +23279,16 @@
         <v>0.96534930739566094</v>
       </c>
       <c r="H36" s="7">
-        <f>2*MEDIAN(G$2:G$6)</f>
-        <v>0.64395925328417292</v>
+        <f>2*MEDIAN(H$2:H$6)</f>
+        <v>499.6662</v>
       </c>
       <c r="I36" s="10">
         <f t="shared" si="22"/>
         <v>0.97096711636603084</v>
       </c>
       <c r="J36" s="7">
-        <f>2*MEDIAN(H$2:H$6)</f>
-        <v>499.6662</v>
+        <f>2*MEDIAN(J$2:J$6)</f>
+        <v>1984.374</v>
       </c>
       <c r="K36" s="10">
         <f t="shared" si="23"/>
